--- a/tests/testdata/excel/ファイル名/[確定]報告書.xlsx
+++ b/tests/testdata/excel/ファイル名/[確定]報告書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9EC2ABE9-4A45-420F-994D-D579ED5A2F5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF3A33AD-4288-45D8-B25D-A12C24F2239E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{6E5B1871-9EAD-4AAC-9742-E6A464D89754}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{D787389A-6BDD-4CF6-8CD2-1C9CECD8F8C3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57FE5C31-B40D-4BC1-8D1A-71506A9DB214}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A59D3F9-44E2-4742-8002-11E0A2A7BAB7}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/ファイル名/[確定]報告書.xlsx
+++ b/tests/testdata/excel/ファイル名/[確定]報告書.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF3A33AD-4288-45D8-B25D-A12C24F2239E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2299DE61-27A3-4FFD-A58D-842DE6AB5720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{D787389A-6BDD-4CF6-8CD2-1C9CECD8F8C3}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{7355AD54-2E1C-4509-AC0B-145DBD1CC658}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A59D3F9-44E2-4742-8002-11E0A2A7BAB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82469874-6E63-48BB-8C52-D43409785F1F}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
